--- a/game18/web.xlsx
+++ b/game18/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="18915" windowHeight="7620"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="7" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>domain</t>
   </si>
@@ -45,34 +45,16 @@
     <t>json</t>
   </si>
   <si>
-    <t>gablets.cloud</t>
-  </si>
-  <si>
-    <t>#d74f75</t>
-  </si>
-  <si>
-    <t>dvergrs.cloud</t>
-  </si>
-  <si>
-    <t>#1e90ff</t>
-  </si>
-  <si>
-    <t>fylfot.cloud</t>
+    <t>play.fylfot.cloud</t>
   </si>
   <si>
     <t>#746097</t>
   </si>
   <si>
-    <t>noctuarys.com</t>
-  </si>
-  <si>
-    <t>#c2849f</t>
-  </si>
-  <si>
-    <t>apricitys.com</t>
-  </si>
-  <si>
-    <t>#8bbb6a</t>
+    <t>sec.fylfot.cloud</t>
+  </si>
+  <si>
+    <t>game.fylfot.cloud</t>
   </si>
   <si>
     <t>paly.sorrel.cloud</t>
@@ -357,7 +339,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="52">
+  <fills count="50">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -450,18 +432,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD74F75"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E90FF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF746097"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -665,7 +635,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -677,6 +647,19 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -810,7 +793,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -822,119 +805,119 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -987,22 +970,19 @@
     <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1429,8 +1409,8 @@
       <c r="A3" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>8</v>
+      <c r="B3" s="19" t="s">
+        <v>6</v>
       </c>
       <c r="D3">
         <v>5</v>
@@ -1441,10 +1421,10 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B4" s="21" t="s">
-        <v>10</v>
+        <v>8</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>6</v>
       </c>
       <c r="D4">
         <v>2</v>
@@ -1454,40 +1434,18 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="18" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5" s="22" t="s">
-        <v>12</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>4</v>
-      </c>
+      <c r="A5" s="20"/>
+      <c r="B5" s="21"/>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6">
-        <v>5</v>
-      </c>
-      <c r="E6">
-        <v>3</v>
-      </c>
+      <c r="A6" s="20"/>
+      <c r="B6" s="22"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="gablets.cloud"/>
-    <hyperlink ref="A3" r:id="rId2" display="dvergrs.cloud"/>
-    <hyperlink ref="A4" r:id="rId3" display="fylfot.cloud"/>
-    <hyperlink ref="A5" r:id="rId4" display="noctuarys.com"/>
-    <hyperlink ref="A6" r:id="rId5" display="apricitys.com"/>
+    <hyperlink ref="A2" r:id="rId1" display="play.fylfot.cloud"/>
+    <hyperlink ref="A3" r:id="rId1" display="sec.fylfot.cloud"/>
+    <hyperlink ref="A4" r:id="rId1" display="game.fylfot.cloud"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
@@ -1522,10 +1480,10 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1536,10 +1494,10 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1550,10 +1508,10 @@
     </row>
     <row r="4" ht="16.5" spans="1:10">
       <c r="A4" s="1" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1562,20 +1520,20 @@
         <v>3</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" ht="16.5" spans="1:10">
       <c r="A5" s="4"/>
       <c r="B5" s="4"/>
       <c r="I5" s="7" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" ht="16.5" spans="1:10">
@@ -1583,10 +1541,10 @@
       <c r="B6" s="4"/>
       <c r="C6" s="9"/>
       <c r="I6" s="10" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J6" s="11" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" ht="16.5" spans="1:10">
@@ -1596,10 +1554,10 @@
       <c r="D7" s="9"/>
       <c r="E7" s="9"/>
       <c r="I7" s="12" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J7" s="13" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -1609,10 +1567,10 @@
       <c r="D8" s="9"/>
       <c r="E8" s="9"/>
       <c r="I8" s="14" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J8" s="15" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -1622,10 +1580,10 @@
       <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="I9" s="16" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J9" s="17" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:10">

--- a/game18/web.xlsx
+++ b/game18/web.xlsx
@@ -4,11 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="21975" windowHeight="13665"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet2" sheetId="7" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="13" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="14" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="15" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="16" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
   <si>
     <t>domain</t>
   </si>
@@ -45,70 +47,100 @@
     <t>json</t>
   </si>
   <si>
-    <t>play.fylfot.cloud</t>
-  </si>
-  <si>
-    <t>#746097</t>
-  </si>
-  <si>
-    <t>sec.fylfot.cloud</t>
-  </si>
-  <si>
-    <t>game.fylfot.cloud</t>
-  </si>
-  <si>
-    <t>paly.sorrel.cloud</t>
-  </si>
-  <si>
-    <t>#bce3fe</t>
-  </si>
-  <si>
-    <t>paly.defenestrate.site</t>
-  </si>
-  <si>
-    <t>#ffa500</t>
-  </si>
-  <si>
-    <t>paly.knapweed.fun</t>
-  </si>
-  <si>
-    <t>#38dbf8</t>
-  </si>
-  <si>
-    <t>#f7ece7</t>
-  </si>
-  <si>
-    <t>#a37070</t>
-  </si>
-  <si>
-    <t>#e2e1dd</t>
-  </si>
-  <si>
-    <t>#4167b1</t>
-  </si>
-  <si>
-    <t>#fafbe6</t>
-  </si>
-  <si>
-    <t>#d62828</t>
-  </si>
-  <si>
-    <t>#c6e6e8</t>
-  </si>
-  <si>
-    <t>#e58889</t>
-  </si>
-  <si>
-    <t>#e3e3e5</t>
-  </si>
-  <si>
-    <t>#b57743</t>
-  </si>
-  <si>
-    <t>#f5f4f7</t>
-  </si>
-  <si>
-    <t>#a61b29</t>
+    <t>play.astralite.cloud</t>
+  </si>
+  <si>
+    <t>#e3a841</t>
+  </si>
+  <si>
+    <t>sec.astralite.cloud</t>
+  </si>
+  <si>
+    <t>#bdd0c4</t>
+  </si>
+  <si>
+    <t>play.lavendula.cloud</t>
+  </si>
+  <si>
+    <t>#ebd86c</t>
+  </si>
+  <si>
+    <t>sec.lavendula.cloud</t>
+  </si>
+  <si>
+    <t>#ffc408</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
+    <t>hfwinfo.top</t>
+  </si>
+  <si>
+    <t>#664b3a</t>
+  </si>
+  <si>
+    <t>jkif.top</t>
+  </si>
+  <si>
+    <t>#e07563</t>
+  </si>
+  <si>
+    <t>mcif.top</t>
+  </si>
+  <si>
+    <t>#41bbcb</t>
+  </si>
+  <si>
+    <t>haberdasher.cloud</t>
+  </si>
+  <si>
+    <t>#fb9966</t>
+  </si>
+  <si>
+    <t>melancholy.cloud</t>
+  </si>
+  <si>
+    <t>#afcd53</t>
+  </si>
+  <si>
+    <t>insulary.fun</t>
+  </si>
+  <si>
+    <t>#ed6d46</t>
+  </si>
+  <si>
+    <t>vapourous.fun</t>
+  </si>
+  <si>
+    <t>#7d929f</t>
+  </si>
+  <si>
+    <t>unsdgaction.com</t>
+  </si>
+  <si>
+    <t>#ddbb99</t>
+  </si>
+  <si>
+    <t>周一</t>
+  </si>
+  <si>
+    <t>周二</t>
+  </si>
+  <si>
+    <t>周三</t>
+  </si>
+  <si>
+    <t>周四</t>
+  </si>
+  <si>
+    <t>周五</t>
+  </si>
+  <si>
+    <t>周六</t>
+  </si>
+  <si>
+    <t>周日</t>
   </si>
 </sst>
 </file>
@@ -121,7 +153,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -130,16 +162,39 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="10"/>
-      <color rgb="FF175CEB"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -147,34 +202,22 @@
     <font>
       <u/>
       <sz val="10"/>
-      <color rgb="FF417FF9"/>
+      <color rgb="FF2972F4"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Microsoft YaHei"/>
+      <color rgb="FF2972F4"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
       <u/>
-      <sz val="9"/>
+      <sz val="10"/>
       <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -188,18 +231,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10.5"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -339,7 +381,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="50">
+  <fills count="46">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -348,103 +390,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFBCE3FE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFA500"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7ECE7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA37070"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE2E1DD"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4167B1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAFBE6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD62828"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6E6E8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE58889"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3E3E5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB57743"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF5F4F7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA61B29"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF746097"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC2849F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8BBB6A"/>
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFB9966"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFCD53"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED6D46"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7D929F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDBB99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF664B3A"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE07563"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41BBCB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3A841"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD0C4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBD86C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC408"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -635,7 +653,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -647,19 +665,6 @@
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="FF000000"/>
       </right>
@@ -772,218 +777,225 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1038,6 +1050,11 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <colors>
+    <mruColors>
+      <color rgb="00F4F207"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1368,13 +1385,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="28.875" customWidth="1"/>
+    <col min="1" max="1" width="26.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1391,62 +1408,95 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="18" t="s">
+    <row r="2" spans="1:6">
+      <c r="A2" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="D2">
+      <c r="C2" s="22"/>
+      <c r="D2" s="3">
         <v>1</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="3">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="18" t="s">
+      <c r="F2" s="3"/>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3">
-        <v>5</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="18" t="s">
+      <c r="B3" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D4">
+      <c r="C3" s="22"/>
+      <c r="D3" s="3">
         <v>2</v>
       </c>
-      <c r="E4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="20"/>
-      <c r="B5" s="21"/>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="20"/>
-      <c r="B6" s="22"/>
+      <c r="E3" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="24" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="3">
+        <v>3</v>
+      </c>
+      <c r="E4" s="3">
+        <v>2</v>
+      </c>
+      <c r="F4" s="3"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="3">
+        <v>4</v>
+      </c>
+      <c r="E5" s="3">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="12"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="12"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="3"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="play.fylfot.cloud"/>
-    <hyperlink ref="A3" r:id="rId1" display="sec.fylfot.cloud"/>
-    <hyperlink ref="A4" r:id="rId1" display="game.fylfot.cloud"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1455,162 +1505,359 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <dimension ref="A1:H20"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="40.875" customWidth="1"/>
+    <col min="1" max="1" width="27.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" ht="16.5" spans="1:10">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="4" t="s">
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-      <c r="E4">
-        <v>3</v>
-      </c>
-      <c r="I4" s="5" t="s">
+      <c r="B2" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="C2" s="12"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="10" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="5" ht="16.5" spans="1:10">
-      <c r="A5" s="4"/>
-      <c r="B5" s="4"/>
-      <c r="I5" s="7" t="s">
+      <c r="B3" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="8" t="s">
+      <c r="C3" s="12"/>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" s="10" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:10">
-      <c r="A6" s="4"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="9"/>
-      <c r="I6" s="10" t="s">
+      <c r="B4" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="11" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:10">
-      <c r="A7" s="9"/>
-      <c r="B7" s="9"/>
-      <c r="C7" s="9"/>
-      <c r="D7" s="9"/>
-      <c r="E7" s="9"/>
-      <c r="I7" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J7" s="13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" s="9"/>
-      <c r="I8" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="J8" s="15" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="I9" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="J9" s="17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="9"/>
-      <c r="B10" s="9"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" s="9"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="16"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="17"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" s="17"/>
+      <c r="B6" s="17"/>
+      <c r="C6" s="15"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" s="12"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="12"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="19"/>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="18"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="18"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="18"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="18"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="18"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" s="18"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" s="18"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" s="18"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="18"/>
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" s="18"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" s="18"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" s="18"/>
+      <c r="B20" s="18"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A7" r:id="rId1"/>
-    <hyperlink ref="A8" r:id="rId2"/>
-    <hyperlink ref="A11" r:id="rId3"/>
-    <hyperlink ref="A5" r:id="rId4" tooltip="http://wkkgame.top"/>
-    <hyperlink ref="A2" r:id="rId5" display="paly.sorrel.cloud" tooltip="http://sorrel.cloud"/>
-    <hyperlink ref="A3" r:id="rId6" display="paly.defenestrate.site" tooltip="http://defenestrate.site"/>
-    <hyperlink ref="A4" r:id="rId7" display="paly.knapweed.fun" tooltip="http://knapweed.fun"/>
+    <hyperlink ref="F16" r:id="rId1"/>
+    <hyperlink ref="F17" r:id="rId2"/>
+    <hyperlink ref="A2" r:id="rId3" display="hfwinfo.top" tooltip="http://hfwinfo.top"/>
+    <hyperlink ref="A3" r:id="rId4" display="jkif.top" tooltip="http://jkif.top"/>
+    <hyperlink ref="A4" r:id="rId5" display="mcif.top" tooltip="http://mcif.top"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="15.375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6">
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A6" r:id="rId1" display="unsdgaction.com" tooltip="https://unsdgaction.com"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:G2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="1" outlineLevelCol="6"/>
+  <sheetData>
+    <row r="1" spans="1:7">
+      <c r="A1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="D2" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/game18/web.xlsx
+++ b/game18/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="21975" windowHeight="13665"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="13" r:id="rId1"/>
@@ -47,28 +47,28 @@
     <t>json</t>
   </si>
   <si>
-    <t>play.astralite.cloud</t>
-  </si>
-  <si>
-    <t>#e3a841</t>
-  </si>
-  <si>
-    <t>sec.astralite.cloud</t>
-  </si>
-  <si>
-    <t>#bdd0c4</t>
-  </si>
-  <si>
-    <t>play.lavendula.cloud</t>
-  </si>
-  <si>
-    <t>#ebd86c</t>
-  </si>
-  <si>
-    <t>sec.lavendula.cloud</t>
-  </si>
-  <si>
-    <t>#ffc408</t>
+    <t>play.ferventness.com</t>
+  </si>
+  <si>
+    <t>#ee819e</t>
+  </si>
+  <si>
+    <t>sec.ferventness.com</t>
+  </si>
+  <si>
+    <t>#d4e5ef</t>
+  </si>
+  <si>
+    <t>play.feverishness.com</t>
+  </si>
+  <si>
+    <t>#718771</t>
+  </si>
+  <si>
+    <t>sec.feverishness.com</t>
+  </si>
+  <si>
+    <t>#73AE52</t>
   </si>
   <si>
     <t>color</t>
@@ -223,16 +223,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="9"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="10.5"/>
       <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10.5"/>
+      <color rgb="FFFBF1D7"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -444,25 +443,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE3A841"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD0C4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEBD86C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC408"/>
+        <fgColor rgb="FFEE819E"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD4E5EF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF718771"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF73AE52"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -922,7 +921,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -979,19 +978,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1415,12 +1411,12 @@
       <c r="B2" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="22"/>
+      <c r="C2" s="3"/>
       <c r="D2" s="3">
         <v>1</v>
       </c>
       <c r="E2" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="3"/>
     </row>
@@ -1428,10 +1424,10 @@
       <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="3"/>
       <c r="D3" s="3">
         <v>2</v>
       </c>
@@ -1444,31 +1440,31 @@
       <c r="A4" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="24" t="s">
+      <c r="B4" s="23" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="22"/>
+      <c r="C4" s="3"/>
       <c r="D4" s="3">
         <v>3</v>
       </c>
       <c r="E4" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="3"/>
     </row>
     <row r="5" spans="1:6">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="22"/>
+      <c r="C5" s="3"/>
       <c r="D5" s="3">
         <v>4</v>
       </c>
       <c r="E5" s="3">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F5" s="3"/>
     </row>
@@ -1497,6 +1493,12 @@
       <c r="F8" s="3"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="play.ferventness.com"/>
+    <hyperlink ref="A3" r:id="rId1" display="sec.ferventness.com"/>
+    <hyperlink ref="A4" r:id="rId2" display="play.feverishness.com"/>
+    <hyperlink ref="A5" r:id="rId2" display="sec.feverishness.com"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
